--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -74,35 +74,12 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1. 安卓
-2. IOS</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Administrator:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1. google 绑定奖励
-2. facebook 绑定奖励
-3. 手机绑定奖励
-4. IOS登入绑定奖励
-5. 登入(注册)奖励
-注：【游客】默认永久存在</t>
+1. 游客
+2. google
+3. ios
+4. facebook 
+5. 手机
+</t>
         </r>
       </text>
     </comment>
@@ -111,14 +88,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>序号ID</t>
   </si>
   <si>
-    <t>设备类型</t>
-  </si>
-  <si>
     <t>奖励类型</t>
   </si>
   <si>
@@ -137,34 +111,28 @@
     <t>id</t>
   </si>
   <si>
-    <t>phoneType</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
     <t>awardItem</t>
   </si>
   <si>
+    <t>游客登入</t>
+  </si>
+  <si>
     <t>google登入</t>
   </si>
   <si>
     <t>1990000_1000000</t>
   </si>
   <si>
+    <t>ios登入</t>
+  </si>
+  <si>
     <t>facebook登入</t>
   </si>
   <si>
     <t>手机登入</t>
-  </si>
-  <si>
-    <t>登陆(注册)奖励</t>
-  </si>
-  <si>
-    <t>1990000_600000</t>
-  </si>
-  <si>
-    <t>ios登入</t>
   </si>
 </sst>
 </file>
@@ -177,7 +145,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -189,6 +157,11 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -693,138 +666,138 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -834,16 +807,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1158,206 +1134,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="4" width="25.2916666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.6416666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2"/>
-    <col min="7" max="7" width="9.375" style="2"/>
-    <col min="8" max="8" width="23.25" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="1" max="3" width="25.2916666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.6416666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9" style="3"/>
+    <col min="6" max="6" width="9.375" style="3"/>
+    <col min="7" max="7" width="23.25" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="15" spans="1:5">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" ht="15" spans="1:5">
-      <c r="A2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="15" spans="1:5">
-      <c r="A3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="5" t="s">
-        <v>10</v>
-      </c>
+    <row r="4" s="1" customFormat="1" ht="15" spans="1:4">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="15" spans="1:5">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5">
+    <row r="5" s="2" customFormat="1" spans="1:3">
       <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:5">
+    <row r="6" s="2" customFormat="1" spans="1:4">
       <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2">
         <v>2</v>
       </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:5">
+    <row r="7" s="2" customFormat="1" spans="1:4">
       <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2">
         <v>3</v>
       </c>
+      <c r="C7" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="D7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" s="2" customFormat="1" spans="1:4">
       <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>1</v>
-      </c>
-      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" spans="1:4">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>16</v>
+      <c r="B9" s="2">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="6">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6">
-        <v>2</v>
-      </c>
-      <c r="C9" s="6">
-        <v>4</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>12</v>
-      </c>
+    <row r="10" s="2" customFormat="1"/>
+    <row r="11" s="2" customFormat="1"/>
+    <row r="12" s="3" customFormat="1" spans="1:4">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:5">
-      <c r="A10" s="6">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6">
-        <v>2</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" spans="1:5">
-      <c r="A11" s="6">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6">
-        <v>3</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="6">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6">
-        <v>2</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>16</v>
-      </c>
+    <row r="13" spans="1:4">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -105,7 +105,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
     <t>id</t>
@@ -329,12 +329,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_1000000</t>
+    <t>1990000_199000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -329,12 +329,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_199000</t>
+    <t>1990000_1400000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -1189,7 +1189,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:3">
+    <row r="5" s="2" customFormat="1" spans="1:4">
       <c r="A5" s="2">
         <v>1</v>
       </c>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_1400000</t>
+    <t>1990000_5200</t>
   </si>
   <si>
     <t>ios登入</t>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>序号ID</t>
   </si>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_5200</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>手机登入</t>
+  </si>
+  <si>
+    <t>1990000_8000</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1142,7 @@
   <cols>
     <col min="1" max="3" width="25.2916666666667" style="3" customWidth="1"/>
     <col min="4" max="4" width="27.6416666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9" style="3"/>
+    <col min="5" max="5" width="14.125" style="3"/>
     <col min="6" max="6" width="9.375" style="3"/>
     <col min="7" max="7" width="23.25" style="3" customWidth="1"/>
     <col min="8" max="16384" width="9" style="3"/>
@@ -1253,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -123,19 +123,19 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_8600</t>
   </si>
   <si>
     <t>ios登入</t>
   </si>
   <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
     <t>facebook登入</t>
   </si>
   <si>
     <t>手机登入</t>
-  </si>
-  <si>
-    <t>1990000_8000</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:4">
@@ -1253,10 +1253,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,19 +123,19 @@
     <t>google登入</t>
   </si>
   <si>
+    <t>1990000_2100</t>
+  </si>
+  <si>
+    <t>ios登入</t>
+  </si>
+  <si>
+    <t>facebook登入</t>
+  </si>
+  <si>
+    <t>手机登入</t>
+  </si>
+  <si>
     <t>1990000_8600</t>
-  </si>
-  <si>
-    <t>ios登入</t>
-  </si>
-  <si>
-    <t>1990000_2100</t>
-  </si>
-  <si>
-    <t>facebook登入</t>
-  </si>
-  <si>
-    <t>手机登入</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1228,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" spans="1:4">
@@ -1239,10 +1239,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" spans="1:4">
@@ -1253,10 +1253,10 @@
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1"/>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2100</t>
+    <t>1990000_2000</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -135,7 +135,7 @@
     <t>手机登入</t>
   </si>
   <si>
-    <t>1990000_8600</t>
+    <t>1990000_8000</t>
   </si>
 </sst>
 </file>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="loginConfig" sheetId="1" r:id="rId1"/>
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2100</t>
+    <t>1990000_21400</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -135,7 +135,7 @@
     <t>手机登入</t>
   </si>
   <si>
-    <t>1990000_8600</t>
+    <t>1990000_85700</t>
   </si>
 </sst>
 </file>

--- a/account/resources/sample/loginConfig.xlsx
+++ b/account/resources/sample/loginConfig.xlsx
@@ -123,7 +123,7 @@
     <t>google登入</t>
   </si>
   <si>
-    <t>1990000_2000</t>
+    <t>1990000_21400</t>
   </si>
   <si>
     <t>ios登入</t>
@@ -135,7 +135,7 @@
     <t>手机登入</t>
   </si>
   <si>
-    <t>1990000_8000</t>
+    <t>1990000_85700</t>
   </si>
 </sst>
 </file>
